--- a/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/outputs_IAEE_2025_run_2024_utilization_share.xlsx
+++ b/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/outputs_IAEE_2025_run_2024_utilization_share.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,309 +449,346 @@
           <t>Share</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>357542.0326588965</v>
+        <v>139365.0872146152</v>
       </c>
       <c r="C2" t="n">
-        <v>385915</v>
+        <v>149481</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9264787133407526</v>
+        <v>0.9323264308816184</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25402</v>
+        <v>183773.7</v>
       </c>
       <c r="C3" t="n">
-        <v>25402</v>
+        <v>183773.7</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>162993.2216790809</v>
+        <v>122125</v>
       </c>
       <c r="C4" t="n">
-        <v>655567</v>
+        <v>122125</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2486293875059008</v>
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>162993.2216790809</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>655567</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.2486293875059008</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36490.41771</v>
+        <v>11669.45083333333</v>
       </c>
       <c r="C6" t="n">
-        <v>39080</v>
+        <v>43965</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9337363794779939</v>
+        <v>0.2654259259259258</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>158153.1530507728</v>
+        <v>357542.0326588965</v>
       </c>
       <c r="C7" t="n">
-        <v>500419.4</v>
+        <v>385915</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3160412107339819</v>
+        <v>0.9264787133407526</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>25402</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>25402</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>90625.03626903141</v>
+        <v>209514.5168147118</v>
       </c>
       <c r="C9" t="n">
-        <v>469937</v>
+        <v>253531.5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1928450755506194</v>
+        <v>0.8263845589787139</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>81091</v>
+        <v>36490.41771</v>
       </c>
       <c r="C10" t="n">
-        <v>81091</v>
+        <v>39080</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0.9337363794779939</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>139365.0872146152</v>
+        <v>11108.45948084762</v>
       </c>
       <c r="C11" t="n">
-        <v>149481</v>
+        <v>14655</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9323264308816184</v>
+        <v>0.7579979174921611</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>183773.7</v>
+        <v>81091</v>
       </c>
       <c r="C12" t="n">
-        <v>183773.7</v>
+        <v>81091</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>209514.5168147118</v>
+        <v>43774.39964126465</v>
       </c>
       <c r="C13" t="n">
-        <v>253531.5</v>
+        <v>74252</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8263845589787139</v>
+        <v>0.5895383241025784</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>158153.1530507728</v>
       </c>
       <c r="C14" t="n">
-        <v>234480</v>
+        <v>500419.4</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.3160412107339819</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11669.45083333333</v>
+        <v>90625.03626903141</v>
       </c>
       <c r="C15" t="n">
-        <v>43965</v>
+        <v>469937</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2654259259259258</v>
+        <v>0.1928450755506194</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11108.45948084762</v>
+        <v>1633627.475352554</v>
       </c>
       <c r="C16" t="n">
-        <v>14655</v>
+        <v>2999194.6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7579979174921611</v>
+        <v>0.5446887225498986</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>Total_EU</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>122125</v>
+        <v>1384849.28603275</v>
       </c>
       <c r="C17" t="n">
-        <v>122125</v>
+        <v>2028838.2</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>PT</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>43774.39964126465</v>
-      </c>
-      <c r="C18" t="n">
-        <v>74252</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.5895383241025784</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1633627.475352554</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3233674.6</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.5051922897104596</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Total_EU</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1384849.28603275</v>
-      </c>
-      <c r="C20" t="n">
-        <v>2263318.2</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.6118668095510167</v>
+        <v>0.6825824188605825</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/outputs_IAEE_2025_run_2024_utilization_share.xlsx
+++ b/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/outputs_IAEE_2025_run_2024_utilization_share.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/outputs_IAEE_2025_run_2024_utilization_share.xlsx
+++ b/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/outputs_IAEE_2025_run_2024_utilization_share.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,17 +500,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>122125</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>122125</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -521,17 +521,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>162993.2216790809</v>
+        <v>122125</v>
       </c>
       <c r="C5" t="n">
-        <v>655567</v>
+        <v>122125</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2486293875059008</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -542,17 +542,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11669.45083333333</v>
+        <v>162993.2216790809</v>
       </c>
       <c r="C6" t="n">
-        <v>43965</v>
+        <v>655567</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2654259259259258</v>
+        <v>0.2486293875059008</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -563,17 +563,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>357542.0326588965</v>
+        <v>11669.45083333333</v>
       </c>
       <c r="C7" t="n">
-        <v>385915</v>
+        <v>43965</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9264787133407526</v>
+        <v>0.2654259259259258</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -584,17 +584,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25402</v>
+        <v>357542.0326588965</v>
       </c>
       <c r="C8" t="n">
-        <v>25402</v>
+        <v>385915</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0.9264787133407526</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -605,17 +605,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>209514.5168147118</v>
+        <v>25402</v>
       </c>
       <c r="C9" t="n">
-        <v>253531.5</v>
+        <v>25402</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8263845589787139</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -626,17 +626,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36490.41771</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>39080</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9337363794779939</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -647,17 +647,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11108.45948084762</v>
+        <v>209514.5168147118</v>
       </c>
       <c r="C11" t="n">
-        <v>14655</v>
+        <v>253531.5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7579979174921611</v>
+        <v>0.8263845589787139</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -668,17 +668,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81091</v>
+        <v>36490.41771</v>
       </c>
       <c r="C12" t="n">
-        <v>81091</v>
+        <v>39080</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.9337363794779939</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -689,17 +689,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>43774.39964126465</v>
+        <v>11108.45948084762</v>
       </c>
       <c r="C13" t="n">
-        <v>74252</v>
+        <v>14655</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5895383241025784</v>
+        <v>0.7579979174921611</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -710,17 +710,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>158153.1530507728</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>500419.4</v>
+        <v>234480</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3160412107339819</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -731,17 +731,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>90625.03626903141</v>
+        <v>81091</v>
       </c>
       <c r="C15" t="n">
-        <v>469937</v>
+        <v>81091</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1928450755506194</v>
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -752,40 +752,103 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1633627.475352554</v>
+        <v>43774.39964126465</v>
       </c>
       <c r="C16" t="n">
-        <v>2999194.6</v>
+        <v>74252</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5446887225498986</v>
+        <v>0.5895383241025784</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>royalblue</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>158153.1530507728</v>
+      </c>
+      <c r="C17" t="n">
+        <v>500419.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3160412107339819</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>90625.03626903141</v>
+      </c>
+      <c r="C18" t="n">
+        <v>469937</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1928450755506194</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1633627.475352554</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3233674.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.5051922897104595</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Total_EU</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B20" t="n">
         <v>1384849.28603275</v>
       </c>
-      <c r="C17" t="n">
-        <v>2028838.2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.6825824188605825</v>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="C20" t="n">
+        <v>2263318.2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6118668095510167</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>orange</t>
         </is>

--- a/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/outputs_IAEE_2025_run_2024_utilization_share.xlsx
+++ b/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/outputs_IAEE_2025_run_2024_utilization_share.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,11 +449,6 @@
           <t>Share</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -470,11 +465,6 @@
       <c r="D2" t="n">
         <v>0.9323264308816184</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -491,11 +481,6 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -512,11 +497,6 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -533,11 +513,6 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -554,11 +529,6 @@
       <c r="D6" t="n">
         <v>0.2486293875059008</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -575,11 +545,6 @@
       <c r="D7" t="n">
         <v>0.2654259259259258</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -596,11 +561,6 @@
       <c r="D8" t="n">
         <v>0.9264787133407526</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -617,11 +577,6 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -638,11 +593,6 @@
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -659,11 +609,6 @@
       <c r="D11" t="n">
         <v>0.8263845589787139</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -680,11 +625,6 @@
       <c r="D12" t="n">
         <v>0.9337363794779939</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -701,11 +641,6 @@
       <c r="D13" t="n">
         <v>0.7579979174921611</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -722,11 +657,6 @@
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -743,11 +673,6 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -764,11 +689,6 @@
       <c r="D16" t="n">
         <v>0.5895383241025784</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -785,11 +705,6 @@
       <c r="D17" t="n">
         <v>0.3160412107339819</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -806,11 +721,6 @@
       <c r="D18" t="n">
         <v>0.1928450755506194</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>royalblue</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -827,11 +737,6 @@
       <c r="D19" t="n">
         <v>0.5051922897104595</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -847,11 +752,6 @@
       </c>
       <c r="D20" t="n">
         <v>0.6118668095510167</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/outputs_IAEE_2025_run_2024_utilization_share.xlsx
+++ b/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/02_prepared_results/outputs_IAEE_2025_run_2024_utilization_share.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,11 @@
           <t>Share</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -465,6 +470,11 @@
       <c r="D2" t="n">
         <v>0.9323264308816184</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -481,6 +491,11 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -497,6 +512,11 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -513,6 +533,11 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -529,6 +554,11 @@
       <c r="D6" t="n">
         <v>0.2486293875059008</v>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -545,6 +575,11 @@
       <c r="D7" t="n">
         <v>0.2654259259259258</v>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -561,6 +596,11 @@
       <c r="D8" t="n">
         <v>0.9264787133407526</v>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -577,6 +617,11 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -593,6 +638,11 @@
       <c r="D10" t="n">
         <v>0</v>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -609,6 +659,11 @@
       <c r="D11" t="n">
         <v>0.8263845589787139</v>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,6 +680,11 @@
       <c r="D12" t="n">
         <v>0.9337363794779939</v>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -641,6 +701,11 @@
       <c r="D13" t="n">
         <v>0.7579979174921611</v>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -657,6 +722,11 @@
       <c r="D14" t="n">
         <v>0</v>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -673,6 +743,11 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -689,6 +764,11 @@
       <c r="D16" t="n">
         <v>0.5895383241025784</v>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -705,6 +785,11 @@
       <c r="D17" t="n">
         <v>0.3160412107339819</v>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -721,6 +806,11 @@
       <c r="D18" t="n">
         <v>0.1928450755506194</v>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>royalblue</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -737,6 +827,11 @@
       <c r="D19" t="n">
         <v>0.5051922897104595</v>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -752,6 +847,11 @@
       </c>
       <c r="D20" t="n">
         <v>0.6118668095510167</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
       </c>
     </row>
   </sheetData>
